--- a/data/trans_camb/P45C_R1-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P45C_R1-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 0,45</t>
+          <t>-3,58; 0,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,98</t>
+          <t>-3,35; 1,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 1,9</t>
+          <t>-3,37; 1,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,1</t>
+          <t>-1,53; 2,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,82</t>
+          <t>-0,79; 3,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,96</t>
+          <t>-1,94; 2,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,62</t>
+          <t>-2,08; 0,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,84</t>
+          <t>-1,2; 1,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,14</t>
+          <t>-2,06; 1,2</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-84,01; 42,64</t>
+          <t>-85,33; 45,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-85,95; 86,0</t>
+          <t>-83,18; 85,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-91,01; 169,18</t>
+          <t>-89,86; 155,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-60,31; 250,59</t>
+          <t>-66,65; 262,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,69; 396,23</t>
+          <t>-38,72; 340,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-95,95; 322,02</t>
+          <t>-95,72; 324,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-67,45; 44,16</t>
+          <t>-70,24; 38,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,01; 133,42</t>
+          <t>-45,28; 128,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-77,88; 79,13</t>
+          <t>-76,7; 92,84</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,57</t>
+          <t>-0,79; 2,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 0,55</t>
+          <t>-2,3; 0,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 3,26</t>
+          <t>-1,36; 3,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,02</t>
+          <t>-1,84; 1,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,68</t>
+          <t>-2,14; 0,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 2,77</t>
+          <t>-1,45; 2,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,45</t>
+          <t>-0,83; 1,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,27</t>
+          <t>-1,68; 0,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,08</t>
+          <t>-0,82; 2,17</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-36,63; 195,32</t>
+          <t>-32,74; 205,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-76,85; 46,35</t>
+          <t>-80,72; 60,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-73,29; 245,31</t>
+          <t>-62,71; 282,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-70,09; 110,22</t>
+          <t>-73,37; 104,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-80,52; 75,49</t>
+          <t>-80,43; 71,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-60,32; 224,03</t>
+          <t>-59,15; 205,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,46; 110,08</t>
+          <t>-35,74; 94,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-68,95; 21,28</t>
+          <t>-68,66; 25,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-39,04; 136,95</t>
+          <t>-40,65; 144,34</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,49</t>
+          <t>-1,27; 0,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,1</t>
+          <t>-0,96; 1,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 2,81</t>
+          <t>-0,22; 2,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 1,22</t>
+          <t>-2,1; 1,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; -1,05</t>
+          <t>-3,73; -0,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,02</t>
+          <t>-2,3; 0,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,61</t>
+          <t>-1,46; 0,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; -0,23</t>
+          <t>-2,02; -0,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,39</t>
+          <t>-0,83; 1,33</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-89,64; 209,6</t>
+          <t>-88,75; 217,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-76,49; 261,04</t>
+          <t>-73,46; 275,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-37,24; 603,2</t>
+          <t>-29,29; 616,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-63,36; 71,18</t>
+          <t>-58,17; 83,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-96,81; -43,21</t>
+          <t>-96,67; -40,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,17; 66,07</t>
+          <t>-63,99; 62,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-60,66; 57,52</t>
+          <t>-60,94; 52,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-83,72; -16,31</t>
+          <t>-82,9; -12,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-35,49; 119,01</t>
+          <t>-39,8; 105,55</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 0,89</t>
+          <t>-2,6; 0,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,74</t>
+          <t>-3,59; -0,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 0,67</t>
+          <t>-3,02; 0,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,35</t>
+          <t>-1,09; 2,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,48</t>
+          <t>-1,7; 1,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,41</t>
+          <t>-1,52; 1,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,12</t>
+          <t>-1,41; 1,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,0</t>
+          <t>-2,19; -0,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,73</t>
+          <t>-1,77; 0,65</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-76,07; 85,79</t>
+          <t>-75,49; 79,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -29,35</t>
+          <t>-100,0; -12,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-82,32; 56,16</t>
+          <t>-83,54; 61,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-42,69; 276,96</t>
+          <t>-48,67; 255,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-63,32; 176,77</t>
+          <t>-68,01; 159,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,68; 205,63</t>
+          <t>-56,1; 163,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-49,96; 88,98</t>
+          <t>-50,9; 92,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-79,84; 6,63</t>
+          <t>-78,92; 1,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-61,13; 60,1</t>
+          <t>-63,38; 49,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,78</t>
+          <t>-1,92; 0,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,08</t>
+          <t>-1,83; 1,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,61</t>
+          <t>-0,74; 2,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,79</t>
+          <t>-2,43; 0,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,5</t>
+          <t>-2,49; 0,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,14</t>
+          <t>-1,89; 1,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,39</t>
+          <t>-1,75; 0,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,44</t>
+          <t>-1,7; 0,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,47</t>
+          <t>-0,74; 1,45</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 209,55</t>
+          <t>-89,58; 300,95</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 378,88</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>-42,87; 446,76</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>-87,3; 180,41</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>-33,11; 494,93</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>-88,99; 113,25</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>-90,37; 101,41</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-67,84; 180,97</t>
+          <t>-68,87; 132,63</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-79,85; 52,2</t>
+          <t>-79,65; 66,03</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-80,3; 60,42</t>
+          <t>-80,06; 78,79</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-39,54; 172,81</t>
+          <t>-38,41; 167,43</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,71</t>
+          <t>-1,74; 1,61</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,71</t>
+          <t>-1,53; 1,98</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,73</t>
+          <t>-2,13; 0,78</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,87</t>
+          <t>-1,02; 1,88</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,99</t>
+          <t>-1,32; 0,83</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,54</t>
+          <t>-1,74; 0,6</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,24</t>
+          <t>-0,84; 1,23</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,9</t>
+          <t>-1,11; 0,88</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,44</t>
+          <t>-1,3; 0,37</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-85,19; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1888,22 +1888,22 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-93,6; 297,81</t>
+          <t>-93,87; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-67,18; 410,37</t>
+          <t>-74,53; 394,84</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-92,54; 290,99</t>
+          <t>-89,14; 276,69</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-86,33; 128,79</t>
+          <t>-83,1; 109,92</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,39</t>
+          <t>-3,64; -0,39</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 0,62</t>
+          <t>-2,78; 0,7</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 0,33</t>
+          <t>-3,13; 0,37</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,4</t>
+          <t>-0,68; 1,42</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,94</t>
+          <t>-0,98; 0,65</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,35</t>
+          <t>-1,53; 0,35</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,35</t>
+          <t>-1,35; 0,36</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,51</t>
+          <t>-1,36; 0,5</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,2</t>
+          <t>-1,39; 0,23</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 351,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-92,25; 150,97</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,16</t>
+          <t>-1,06; 0,15</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,37; -0,21</t>
+          <t>-1,38; -0,22</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,55</t>
+          <t>-0,81; 0,66</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,55</t>
+          <t>-0,72; 0,55</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,04</t>
+          <t>-1,12; 0,01</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,31</t>
+          <t>-0,9; 0,34</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,19</t>
+          <t>-0,7; 0,23</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,07; -0,28</t>
+          <t>-1,1; -0,28</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,32</t>
+          <t>-0,65; 0,28</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-49,18; 13,58</t>
+          <t>-50,24; 13,51</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-66,82; -12,07</t>
+          <t>-66,36; -11,82</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-40,09; 41,18</t>
+          <t>-41,27; 49,01</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 38,2</t>
+          <t>-35,26; 39,83</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-54,64; 3,5</t>
+          <t>-55,31; 4,55</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-43,02; 24,5</t>
+          <t>-44,33; 25,12</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-34,99; 13,59</t>
+          <t>-35,53; 15,77</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-55,98; -18,82</t>
+          <t>-55,61; -17,9</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-30,69; 21,06</t>
+          <t>-34,67; 19,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P45C_R1-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P45C_R1-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,12</t>
+          <t>-1,19</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,7</t>
+          <t>-0,43</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 0,24</t>
+          <t>-3,67; 0,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 1,0</t>
+          <t>-3,22; 1,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,83</t>
+          <t>-3,35; 1,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,25</t>
+          <t>-1,51; 2,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,46</t>
+          <t>-0,44; 3,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 2,47</t>
+          <t>-1,63; 3,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,55</t>
+          <t>-1,94; 0,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,79</t>
+          <t>-1,43; 1,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,2</t>
+          <t>-1,91; 1,23</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-41,21%</t>
+          <t>-44,04%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-16,84%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-31,82%</t>
+          <t>-19,62%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-85,33; 45,36</t>
+          <t>-85,9; 43,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-83,18; 85,02</t>
+          <t>-83,23; 104,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-89,86; 155,65</t>
+          <t>-90,15; 145,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-66,65; 262,31</t>
+          <t>-65,0; 222,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 340,08</t>
+          <t>-28,76; 412,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-95,72; 324,15</t>
+          <t>-79,48; 395,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-70,24; 38,93</t>
+          <t>-67,89; 55,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,28; 128,85</t>
+          <t>-48,58; 102,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-76,7; 92,84</t>
+          <t>-71,13; 89,77</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,28</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,59</t>
+          <t>-0,98; 2,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,69</t>
+          <t>-2,14; 0,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 3,3</t>
+          <t>-1,82; 2,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,03</t>
+          <t>-1,74; 1,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,68</t>
+          <t>-2,03; 0,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 2,57</t>
+          <t>-1,25; 2,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,33</t>
+          <t>-0,78; 1,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,29</t>
+          <t>-1,55; 0,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,17</t>
+          <t>-0,98; 1,77</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,74; 205,26</t>
+          <t>-42,31; 205,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-80,72; 60,76</t>
+          <t>-78,83; 56,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-62,71; 282,81</t>
+          <t>-77,62; 185,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-73,37; 104,27</t>
+          <t>-68,51; 104,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-80,43; 71,61</t>
+          <t>-79,21; 68,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,15; 205,78</t>
+          <t>-50,73; 233,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,74; 94,87</t>
+          <t>-33,78; 98,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-68,66; 25,46</t>
+          <t>-66,25; 19,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-40,65; 144,34</t>
+          <t>-40,98; 126,53</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,6</t>
+          <t>-0,81</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,08</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,53</t>
+          <t>-1,3; 0,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,09</t>
+          <t>-0,87; 1,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 2,77</t>
+          <t>-0,25; 2,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,34</t>
+          <t>-2,19; 1,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; -0,98</t>
+          <t>-3,73; -1,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,96</t>
+          <t>-2,37; 0,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,65</t>
+          <t>-1,44; 0,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; -0,25</t>
+          <t>-2,05; -0,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,33</t>
+          <t>-1,04; 1,23</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121,85%</t>
+          <t>112,84%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-23,1%</t>
+          <t>-30,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-88,75; 217,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-73,46; 275,76</t>
+          <t>-66,59; 298,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 616,0</t>
+          <t>-40,09; 615,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-58,17; 83,87</t>
+          <t>-59,95; 90,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-96,67; -40,47</t>
+          <t>-96,14; -43,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-63,99; 62,41</t>
+          <t>-65,49; 61,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-60,94; 52,82</t>
+          <t>-59,69; 56,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-82,9; -12,41</t>
+          <t>-83,45; -17,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-39,8; 105,55</t>
+          <t>-45,12; 99,57</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,86</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,41</t>
+          <t>0,09</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 0,96</t>
+          <t>-2,56; 0,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,59; -0,68</t>
+          <t>-3,81; -0,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 0,75</t>
+          <t>-2,13; 1,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,28</t>
+          <t>-1,01; 2,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 1,28</t>
+          <t>-1,67; 1,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,32</t>
+          <t>-1,46; 1,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,1</t>
+          <t>-1,26; 1,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,19; -0,03</t>
+          <t>-2,15; 0,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,65</t>
+          <t>-0,99; 1,18</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-38,4%</t>
+          <t>-2,59%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-20,98%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-75,49; 79,04</t>
+          <t>-74,8; 75,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -12,37</t>
+          <t>-100,0; -30,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-83,54; 61,15</t>
+          <t>-63,2; 126,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-48,67; 255,67</t>
+          <t>-47,98; 224,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-68,01; 159,84</t>
+          <t>-69,8; 145,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-56,1; 163,99</t>
+          <t>-56,03; 179,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-50,9; 92,47</t>
+          <t>-48,35; 91,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-78,92; 1,43</t>
+          <t>-79,08; 12,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-63,38; 49,1</t>
+          <t>-40,36; 89,68</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,27</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,78</t>
+          <t>-2,05; 0,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,21</t>
+          <t>-2,03; 0,98</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,48</t>
+          <t>-0,9; 2,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,96</t>
+          <t>-2,42; 0,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,47</t>
+          <t>-2,45; 0,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,09</t>
+          <t>-1,98; 1,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,43</t>
+          <t>-1,75; 0,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,58</t>
+          <t>-1,79; 0,44</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,45</t>
+          <t>-0,79; 1,28</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-13,51%</t>
+          <t>-14,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-89,58; 300,95</t>
+          <t>-100,0; 263,9</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 378,88</t>
+          <t>-100,0; 289,56</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-42,87; 446,76</t>
+          <t>-53,91; 401,93</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-87,3; 180,41</t>
+          <t>-89,86; 100,55</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,76; 100,39</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-68,87; 132,63</t>
+          <t>-65,17; 174,51</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-79,65; 66,03</t>
+          <t>-81,36; 45,34</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-80,06; 78,79</t>
+          <t>-81,3; 70,63</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-38,41; 167,43</t>
+          <t>-39,16; 155,24</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>-0,06</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,61</t>
+          <t>-1,7; 1,58</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 1,98</t>
+          <t>-1,5; 1,95</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,78</t>
+          <t>-1,92; 0,93</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,88</t>
+          <t>-1,04; 1,82</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,83</t>
+          <t>-1,34; 0,84</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,6</t>
+          <t>-1,43; 0,82</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,23</t>
+          <t>-0,82; 1,31</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,88</t>
+          <t>-1,12; 0,9</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,37</t>
+          <t>-1,0; 0,75</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-27,24%</t>
+          <t>-10,75%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-34,6%</t>
+          <t>-5,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-31,86%</t>
+          <t>-8,08%</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1888,22 +1888,22 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-93,87; —</t>
+          <t>-90,51; 386,88</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-74,53; 394,84</t>
+          <t>-69,07; 465,15</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-89,14; 276,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-83,1; 109,92</t>
+          <t>-72,85; 261,73</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,82</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>-0,39</t>
         </is>
       </c>
     </row>
@@ -1973,22 +1973,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,64; -0,39</t>
+          <t>-3,91; -0,39</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,7</t>
+          <t>-2,94; 0,68</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 0,37</t>
+          <t>-3,13; 0,28</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,42</t>
+          <t>-0,69; 1,38</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1998,22 +1998,22 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,35</t>
+          <t>-1,31; 0,34</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,36</t>
+          <t>-1,4; 0,35</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,5</t>
+          <t>-1,28; 0,63</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,23</t>
+          <t>-1,36; 0,18</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-61,44%</t>
+          <t>-62,55%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-32,46%</t>
+          <t>-34,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-52,93%</t>
+          <t>-54,14%</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-92,25; 150,97</t>
+          <t>-93,51; 136,77</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,06</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,15</t>
+          <t>-1,03; 0,23</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,38; -0,22</t>
+          <t>-1,44; -0,16</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,66</t>
+          <t>-0,65; 0,75</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,55</t>
+          <t>-0,7; 0,54</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,01</t>
+          <t>-1,06; 0,05</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,34</t>
+          <t>-0,66; 0,5</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,23</t>
+          <t>-0,67; 0,22</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,1; -0,28</t>
+          <t>-1,08; -0,28</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,28</t>
+          <t>-0,47; 0,4</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-5,07%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-15,48%</t>
+          <t>-7,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-10,41%</t>
+          <t>-3,45%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-50,24; 13,51</t>
+          <t>-50,63; 19,67</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-66,36; -11,82</t>
+          <t>-68,28; -11,51</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-41,27; 49,01</t>
+          <t>-33,46; 54,08</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-35,26; 39,83</t>
+          <t>-34,88; 40,05</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-55,31; 4,55</t>
+          <t>-54,82; 3,57</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-44,33; 25,12</t>
+          <t>-33,96; 36,95</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-35,53; 15,77</t>
+          <t>-34,16; 15,21</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-55,61; -17,9</t>
+          <t>-55,67; -18,33</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-34,67; 19,26</t>
+          <t>-25,13; 28,54</t>
         </is>
       </c>
     </row>
